--- a/output/full_scan/batch_seq1_2026-08-25.xlsx
+++ b/output/full_scan/batch_seq1_2026-08-25.xlsx
@@ -4460,7 +4460,7 @@
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>247.357910833563</v>
+        <v>247.3579108335629</v>
       </c>
       <c r="E76" s="2" t="n">
         <v>18.45</v>
